--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-06-2025.xlsx
@@ -538,12 +538,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/25mm-celotex-tb3025-2-4m-x-1-2m (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001EAB67A0590&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/25mm-celotex-tb3025-2-4m-x-1-2m (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001EAB820F810&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='diybuildingsupplies.co.uk', port=443): Max retries exceeded with url: /products/celotex-xr4150-high-performance-pir-insulation-2400-x-1200-x-150mm (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001EAB8D998D0&gt;, 'Connection to diybuildingsupplies.co.uk timed out. (connect timeout=None)'))</t>
+          <t>£47.07</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-pl4000-thermal-laminate-insulation-board?variant=55597627408768 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001EAB8DD85D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>£29.79</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£1,225.00</t>
+          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/thermaclass-cavity-wall-21?variant=39698151342133 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002031685EA90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
